--- a/footwear_sneaker_brands_master_analysis.xlsx
+++ b/footwear_sneaker_brands_master_analysis.xlsx
@@ -121,7 +121,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="21">
     <fill>
       <patternFill/>
     </fill>
@@ -203,6 +203,26 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6F7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -230,7 +250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -377,6 +397,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1051,27 +1089,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Deduped Creator Profiles — Full Profile Metrics (91 Creators across Skechers India, Gully Labs, Comet)</t>
+          <t>Deduped Creator Profiles &amp; Tier Classification (91 Creators across Skechers India, Gully Labs, Comet)</t>
         </is>
       </c>
     </row>
@@ -1088,56 +1127,61 @@
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
+          <t>Creator Tier / Size</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
           <t>Brands Collaborated With</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Full Name</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Business / Pro</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>Total Followers</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>Following</t>
         </is>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="J2" s="20" t="inlineStr">
         <is>
           <t>Total Posts</t>
         </is>
       </c>
-      <c r="J2" s="20" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>Avg Likes / Post</t>
         </is>
       </c>
-      <c r="K2" s="20" t="inlineStr">
+      <c r="L2" s="20" t="inlineStr">
         <is>
           <t>Avg Comments / Post</t>
         </is>
       </c>
-      <c r="L2" s="20" t="inlineStr">
+      <c r="M2" s="20" t="inlineStr">
         <is>
           <t>Avg Profile ER%</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="21" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1146,46 +1190,51 @@
           <t>@kartikaaryan</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>KARTIK AARYAN</t>
         </is>
       </c>
-      <c r="E3" s="21" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="H3" s="13" t="n">
         <v>50294891</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="I3" s="13" t="n">
         <v>1289</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="J3" s="13" t="n">
         <v>3388</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="K3" s="13" t="n">
         <v>138004</v>
       </c>
-      <c r="K3" s="13" t="n">
+      <c r="L3" s="13" t="n">
         <v>1359</v>
       </c>
-      <c r="L3" s="14" t="n">
+      <c r="M3" s="14" t="n">
         <v>0.0028</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="21" customHeight="1">
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
@@ -1194,46 +1243,51 @@
           <t>@ananyapanday</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>Ananya 🌙</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="H4" s="13" t="n">
         <v>26281819</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="I4" s="13" t="n">
         <v>1613</v>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="J4" s="13" t="n">
         <v>1737</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="K4" s="13" t="n">
         <v>67476</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="L4" s="13" t="n">
         <v>1274</v>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="M4" s="14" t="n">
         <v>0.0026</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="21" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1242,46 +1296,51 @@
           <t>@surya_14kumar</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Surya Kumar Yadav (SKY)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="H5" s="13" t="n">
         <v>20366023</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="I5" s="13" t="n">
         <v>592</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="J5" s="13" t="n">
         <v>1291</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="K5" s="13" t="n">
         <v>702391</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="L5" s="13" t="n">
         <v>3299</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="M5" s="14" t="n">
         <v>0.0347</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="21" customHeight="1">
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
@@ -1290,46 +1349,51 @@
           <t>@royalenfield</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C6" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
           <t>Royal Enfield</t>
         </is>
       </c>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>3769746</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="I6" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="J6" s="13" t="n">
         <v>5873</v>
       </c>
-      <c r="J6" s="13" t="n">
+      <c r="K6" s="13" t="n">
         <v>12225</v>
       </c>
-      <c r="K6" s="13" t="n">
+      <c r="L6" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="M6" s="14" t="n">
         <v>0.0032</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="21" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1338,46 +1402,51 @@
           <t>@thevishnukaushal</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Vishnu Kaushal</t>
         </is>
       </c>
-      <c r="E7" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>2104862</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="I7" s="13" t="n">
         <v>1113</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="J7" s="13" t="n">
         <v>1568</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="K7" s="13" t="n">
         <v>227869</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="L7" s="13" t="n">
         <v>1093</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="M7" s="14" t="n">
         <v>0.1088</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="21" customHeight="1">
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
@@ -1386,46 +1455,51 @@
           <t>@alayaf</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>ALAYA F</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>2073808</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="13" t="n">
         <v>1165</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="J8" s="13" t="n">
         <v>1046</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="K8" s="13" t="n">
         <v>19593</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="L8" s="13" t="n">
         <v>320</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="M8" s="14" t="n">
         <v>0.009599999999999999</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="21" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1434,46 +1508,51 @@
           <t>@sharktank.india</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C9" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
           <t>Shark Tank India</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>1547638</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="I9" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="I9" s="13" t="n">
+      <c r="J9" s="13" t="n">
         <v>3191</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="K9" s="13" t="n">
         <v>11794</v>
       </c>
-      <c r="K9" s="13" t="n">
+      <c r="L9" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="L9" s="14" t="n">
+      <c r="M9" s="14" t="n">
         <v>0.0077</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="21" customHeight="1">
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
@@ -1482,46 +1561,51 @@
           <t>@bhaiyajiismile</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Sonal Devraj</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F10" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>1118123</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="I10" s="13" t="n">
         <v>2009</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="J10" s="13" t="n">
         <v>1192</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="K10" s="13" t="n">
         <v>5595</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="L10" s="13" t="n">
         <v>69</v>
       </c>
-      <c r="L10" s="14" t="n">
+      <c r="M10" s="14" t="n">
         <v>0.0051</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="21" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1530,46 +1614,51 @@
           <t>@aryankatoch17</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C11" s="50" t="inlineStr">
+        <is>
+          <t>🌟 Mega Creator / Celebrity (1M+)</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
           <t>Aryan Katoch</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>1103182</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="I11" s="13" t="n">
         <v>1852</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="J11" s="13" t="n">
         <v>360</v>
       </c>
-      <c r="J11" s="13" t="n">
+      <c r="K11" s="13" t="n">
         <v>75443</v>
       </c>
-      <c r="K11" s="13" t="n">
+      <c r="L11" s="13" t="n">
         <v>1158</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="M11" s="14" t="n">
         <v>0.0694</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="21" customHeight="1">
       <c r="A12" s="3" t="n">
         <v>10</v>
       </c>
@@ -1578,46 +1667,51 @@
           <t>@cartoon_snacks</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
           <t>Cartoon Snacks</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>859392</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="I12" s="13" t="n">
         <v>271</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="J12" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="K12" s="13" t="n">
         <v>125543</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="L12" s="13" t="n">
         <v>334</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="M12" s="14" t="n">
         <v>0.1465</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="21" customHeight="1">
       <c r="A13" s="3" t="n">
         <v>11</v>
       </c>
@@ -1626,46 +1720,51 @@
           <t>@rashmeetkaur</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
           <t>RASHMEET KAUR</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>836917</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="I13" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="13" t="n">
+      <c r="J13" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="J13" s="13" t="n">
+      <c r="K13" s="13" t="n">
         <v>16968</v>
       </c>
-      <c r="K13" s="13" t="n">
+      <c r="L13" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="M13" s="14" t="n">
         <v>0.0204</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="21" customHeight="1">
       <c r="A14" s="3" t="n">
         <v>12</v>
       </c>
@@ -1674,46 +1773,51 @@
           <t>@gullycricket_in</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
           <t>Gully Crickett</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>630625</v>
       </c>
-      <c r="H14" s="13" t="n">
+      <c r="I14" s="13" t="n">
         <v>227</v>
       </c>
-      <c r="I14" s="13" t="n">
+      <c r="J14" s="13" t="n">
         <v>419</v>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="K14" s="13" t="n">
         <v>33824</v>
       </c>
-      <c r="K14" s="13" t="n">
+      <c r="L14" s="13" t="n">
         <v>157</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="M14" s="14" t="n">
         <v>0.0539</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="21" customHeight="1">
       <c r="A15" s="3" t="n">
         <v>13</v>
       </c>
@@ -1722,46 +1826,51 @@
           <t>@theclassyfoodophile</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
           <t>Pavitra Kaur</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>560101</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="I15" s="13" t="n">
         <v>2326</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="J15" s="13" t="n">
         <v>3707</v>
       </c>
-      <c r="J15" s="13" t="n">
+      <c r="K15" s="13" t="n">
         <v>6727</v>
       </c>
-      <c r="K15" s="13" t="n">
+      <c r="L15" s="13" t="n">
         <v>116</v>
       </c>
-      <c r="L15" s="14" t="n">
+      <c r="M15" s="14" t="n">
         <v>0.0122</v>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="21" customHeight="1">
       <c r="A16" s="3" t="n">
         <v>14</v>
       </c>
@@ -1770,46 +1879,51 @@
           <t>@anyasinghofficial</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D16" s="15" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>Anyaa Singh</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>517516</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="I16" s="13" t="n">
         <v>1196</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="J16" s="13" t="n">
         <v>313</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="K16" s="13" t="n">
         <v>16700</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="L16" s="13" t="n">
         <v>79</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="M16" s="14" t="n">
         <v>0.03240000000000001</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="21" customHeight="1">
       <c r="A17" s="3" t="n">
         <v>15</v>
       </c>
@@ -1818,46 +1932,51 @@
           <t>@officialraga</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
           <t>RAGA</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>489912</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="I17" s="13" t="n">
         <v>963</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="J17" s="13" t="n">
         <v>979</v>
       </c>
-      <c r="J17" s="13" t="n">
+      <c r="K17" s="13" t="n">
         <v>20288</v>
       </c>
-      <c r="K17" s="13" t="n">
+      <c r="L17" s="13" t="n">
         <v>152</v>
       </c>
-      <c r="L17" s="14" t="n">
+      <c r="M17" s="14" t="n">
         <v>0.0417</v>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="21" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>16</v>
       </c>
@@ -1866,46 +1985,51 @@
           <t>@anikjaindesign</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
           <t>Anik Jain</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>480418</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="I18" s="13" t="n">
         <v>1801</v>
       </c>
-      <c r="I18" s="13" t="n">
+      <c r="J18" s="13" t="n">
         <v>1257</v>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="K18" s="13" t="n">
         <v>3828</v>
       </c>
-      <c r="K18" s="13" t="n">
+      <c r="L18" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="M18" s="14" t="n">
         <v>0.008100000000000001</v>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="21" customHeight="1">
       <c r="A19" s="3" t="n">
         <v>17</v>
       </c>
@@ -1914,46 +2038,51 @@
           <t>@hamidbarkzi07</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Hamid Barkzi</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>388435</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="I19" s="13" t="n">
         <v>1091</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="J19" s="13" t="n">
         <v>1461</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="K19" s="13" t="n">
         <v>768</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="L19" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="M19" s="14" t="n">
         <v>0.002</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="21" customHeight="1">
       <c r="A20" s="3" t="n">
         <v>18</v>
       </c>
@@ -1962,46 +2091,51 @@
           <t>@yesmallika</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
           <t>Mallika Motiramani</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F20" s="21" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>381433</v>
       </c>
-      <c r="H20" s="13" t="n">
+      <c r="I20" s="13" t="n">
         <v>1007</v>
       </c>
-      <c r="I20" s="13" t="n">
+      <c r="J20" s="13" t="n">
         <v>462</v>
       </c>
-      <c r="J20" s="13" t="n">
+      <c r="K20" s="13" t="n">
         <v>10602</v>
       </c>
-      <c r="K20" s="13" t="n">
+      <c r="L20" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="M20" s="14" t="n">
         <v>0.0279</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="21" customHeight="1">
       <c r="A21" s="3" t="n">
         <v>19</v>
       </c>
@@ -2010,46 +2144,51 @@
           <t>@harteerathsingh</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C21" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
           <t>Harteerath Singh Ahluwalia</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>335930</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="I21" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="I21" s="13" t="n">
+      <c r="J21" s="13" t="n">
         <v>1083</v>
       </c>
-      <c r="J21" s="13" t="n">
+      <c r="K21" s="13" t="n">
         <v>1533</v>
       </c>
-      <c r="K21" s="13" t="n">
+      <c r="L21" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="M21" s="14" t="n">
         <v>0.004699999999999999</v>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="21" customHeight="1">
       <c r="A22" s="3" t="n">
         <v>20</v>
       </c>
@@ -2058,46 +2197,51 @@
           <t>@sameoldseth</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C22" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
           <t>Seth Eaton</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>243090</v>
       </c>
-      <c r="H22" s="13" t="n">
+      <c r="I22" s="13" t="n">
         <v>3211</v>
       </c>
-      <c r="I22" s="13" t="n">
+      <c r="J22" s="13" t="n">
         <v>858</v>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="K22" s="13" t="n">
         <v>14104</v>
       </c>
-      <c r="K22" s="13" t="n">
+      <c r="L22" s="13" t="n">
         <v>124</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="M22" s="14" t="n">
         <v>0.0585</v>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="21" customHeight="1">
       <c r="A23" s="3" t="n">
         <v>21</v>
       </c>
@@ -2106,46 +2250,51 @@
           <t>@winonakicks</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C23" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
           <t>Charley McClay</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>231074</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="I23" s="13" t="n">
         <v>2155</v>
       </c>
-      <c r="I23" s="13" t="n">
+      <c r="J23" s="13" t="n">
         <v>1110</v>
       </c>
-      <c r="J23" s="13" t="n">
+      <c r="K23" s="13" t="n">
         <v>37430</v>
       </c>
-      <c r="K23" s="13" t="n">
+      <c r="L23" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="M23" s="14" t="n">
         <v>0.1625</v>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="21" customHeight="1">
       <c r="A24" s="3" t="n">
         <v>22</v>
       </c>
@@ -2154,46 +2303,51 @@
           <t>@hemkunt_foundation</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
           <t>Hemkunt Foundation</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>230727</v>
       </c>
-      <c r="H24" s="13" t="n">
+      <c r="I24" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I24" s="13" t="n">
+      <c r="J24" s="13" t="n">
         <v>1401</v>
       </c>
-      <c r="J24" s="13" t="n">
+      <c r="K24" s="13" t="n">
         <v>415</v>
       </c>
-      <c r="K24" s="13" t="n">
+      <c r="L24" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="L24" s="14" t="n">
+      <c r="M24" s="14" t="n">
         <v>0.0019</v>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="21" customHeight="1">
       <c r="A25" s="3" t="n">
         <v>23</v>
       </c>
@@ -2202,46 +2356,51 @@
           <t>@smartkicksofficial</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C25" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
           <t>Amit Pandey • India’s Sneaker Expert &amp; Culture Creator</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>200449</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="I25" s="13" t="n">
         <v>202</v>
       </c>
-      <c r="I25" s="13" t="n">
+      <c r="J25" s="13" t="n">
         <v>1201</v>
       </c>
-      <c r="J25" s="13" t="n">
+      <c r="K25" s="13" t="n">
         <v>38041</v>
       </c>
-      <c r="K25" s="13" t="n">
+      <c r="L25" s="13" t="n">
         <v>209</v>
       </c>
-      <c r="L25" s="14" t="n">
+      <c r="M25" s="14" t="n">
         <v>0.1908</v>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="21" customHeight="1">
       <c r="A26" s="3" t="n">
         <v>24</v>
       </c>
@@ -2250,46 +2409,51 @@
           <t>@itskivitime</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
           <t>Kriti Vij and Viren Barman</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>190473</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="I26" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="J26" s="13" t="n">
         <v>905</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="K26" s="13" t="n">
         <v>3543</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="L26" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="L26" s="14" t="n">
+      <c r="M26" s="14" t="n">
         <v>0.0188</v>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="21" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>25</v>
       </c>
@@ -2298,46 +2462,51 @@
           <t>@i.sahaj</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Sahaj Singh</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="H27" s="13" t="n">
         <v>183147</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="I27" s="13" t="n">
         <v>1821</v>
       </c>
-      <c r="I27" s="13" t="n">
+      <c r="J27" s="13" t="n">
         <v>2813</v>
       </c>
-      <c r="J27" s="13" t="n">
+      <c r="K27" s="13" t="n">
         <v>829</v>
       </c>
-      <c r="K27" s="13" t="n">
+      <c r="L27" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="L27" s="14" t="n">
+      <c r="M27" s="14" t="n">
         <v>0.0048</v>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="3" t="n">
         <v>26</v>
       </c>
@@ -2346,46 +2515,51 @@
           <t>@capt_dvs</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
         <is>
           <t>Capt. Dharmveer Singh</t>
         </is>
       </c>
-      <c r="E28" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>173074</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="I28" s="13" t="n">
         <v>7094</v>
       </c>
-      <c r="I28" s="13" t="n">
+      <c r="J28" s="13" t="n">
         <v>2075</v>
       </c>
-      <c r="J28" s="13" t="n">
+      <c r="K28" s="13" t="n">
         <v>1411</v>
       </c>
-      <c r="K28" s="13" t="n">
+      <c r="L28" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="L28" s="14" t="n">
+      <c r="M28" s="14" t="n">
         <v>0.008500000000000001</v>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
+    <row r="29" ht="21" customHeight="1">
       <c r="A29" s="3" t="n">
         <v>27</v>
       </c>
@@ -2394,46 +2568,51 @@
           <t>@anuj.mp4</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C29" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
           <t>Anuj Gupta</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>156713</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="I29" s="13" t="n">
         <v>992</v>
       </c>
-      <c r="I29" s="13" t="n">
+      <c r="J29" s="13" t="n">
         <v>257</v>
       </c>
-      <c r="J29" s="13" t="n">
+      <c r="K29" s="13" t="n">
         <v>2773</v>
       </c>
-      <c r="K29" s="13" t="n">
+      <c r="L29" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="L29" s="14" t="n">
+      <c r="M29" s="14" t="n">
         <v>0.0179</v>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="21" customHeight="1">
       <c r="A30" s="3" t="n">
         <v>28</v>
       </c>
@@ -2442,46 +2621,51 @@
           <t>@agamjotsingh_10</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
           <t>Agamjot Singh</t>
         </is>
       </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>156634</v>
       </c>
-      <c r="H30" s="13" t="n">
+      <c r="I30" s="13" t="n">
         <v>1217</v>
       </c>
-      <c r="I30" s="13" t="n">
+      <c r="J30" s="13" t="n">
         <v>384</v>
       </c>
-      <c r="J30" s="13" t="n">
+      <c r="K30" s="13" t="n">
         <v>2386</v>
       </c>
-      <c r="K30" s="13" t="n">
+      <c r="L30" s="13" t="n">
         <v>35</v>
       </c>
-      <c r="L30" s="14" t="n">
+      <c r="M30" s="14" t="n">
         <v>0.0155</v>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="21" customHeight="1">
       <c r="A31" s="3" t="n">
         <v>29</v>
       </c>
@@ -2490,46 +2674,51 @@
           <t>@parisa.barkzi</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Parisa Barkzi</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="F31" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="H31" s="13" t="n">
         <v>151512</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="I31" s="13" t="n">
         <v>996</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="J31" s="13" t="n">
         <v>1562</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="K31" s="13" t="n">
         <v>544</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="L31" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="L31" s="14" t="n">
+      <c r="M31" s="14" t="n">
         <v>0.004</v>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="21" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>30</v>
       </c>
@@ -2538,46 +2727,51 @@
           <t>@eeeeshika</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C32" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
           <t>Eshika Tahilramani</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="F32" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F32" s="21" t="inlineStr">
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>140884</v>
       </c>
-      <c r="H32" s="13" t="n">
+      <c r="I32" s="13" t="n">
         <v>1339</v>
       </c>
-      <c r="I32" s="13" t="n">
+      <c r="J32" s="13" t="n">
         <v>903</v>
       </c>
-      <c r="J32" s="13" t="n">
+      <c r="K32" s="13" t="n">
         <v>2641</v>
       </c>
-      <c r="K32" s="13" t="n">
+      <c r="L32" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="L32" s="14" t="n">
+      <c r="M32" s="14" t="n">
         <v>0.0189</v>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" ht="21" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>31</v>
       </c>
@@ -2586,46 +2780,51 @@
           <t>@peachrinq</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C33" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
           <t>Shaima</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="F33" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="H33" s="13" t="n">
         <v>138345</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="I33" s="13" t="n">
         <v>675</v>
       </c>
-      <c r="I33" s="13" t="n">
+      <c r="J33" s="13" t="n">
         <v>257</v>
       </c>
-      <c r="J33" s="13" t="n">
+      <c r="K33" s="13" t="n">
         <v>3976</v>
       </c>
-      <c r="K33" s="13" t="n">
+      <c r="L33" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="L33" s="14" t="n">
+      <c r="M33" s="14" t="n">
         <v>0.029</v>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="21" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>32</v>
       </c>
@@ -2634,46 +2833,51 @@
           <t>@subkocoffee</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
           <t>Subko Coffee Roasters</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="H34" s="13" t="n">
         <v>119642</v>
       </c>
-      <c r="H34" s="13" t="n">
+      <c r="I34" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="I34" s="13" t="n">
+      <c r="J34" s="13" t="n">
         <v>857</v>
       </c>
-      <c r="J34" s="13" t="n">
+      <c r="K34" s="13" t="n">
         <v>1855</v>
       </c>
-      <c r="K34" s="13" t="n">
+      <c r="L34" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="L34" s="14" t="n">
+      <c r="M34" s="14" t="n">
         <v>0.0156</v>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="21" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>33</v>
       </c>
@@ -2682,46 +2886,51 @@
           <t>@rishiudapurkar</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C35" s="52" t="inlineStr">
+        <is>
+          <t>🚀 Macro Creator (100K - 1M)</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
           <t>Rishi Udapurkar</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>113651</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="I35" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="I35" s="13" t="n">
+      <c r="J35" s="13" t="n">
         <v>216</v>
       </c>
-      <c r="J35" s="13" t="n">
+      <c r="K35" s="13" t="n">
         <v>4490</v>
       </c>
-      <c r="K35" s="13" t="n">
+      <c r="L35" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="L35" s="14" t="n">
+      <c r="M35" s="14" t="n">
         <v>0.0397</v>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="21" customHeight="1">
       <c r="A36" s="3" t="n">
         <v>34</v>
       </c>
@@ -2730,46 +2939,51 @@
           <t>@unoindiaofficial</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>UNO India</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F36" s="21" t="inlineStr">
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="H36" s="13" t="n">
         <v>110348</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="I36" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="13" t="n">
+      <c r="J36" s="13" t="n">
         <v>457</v>
       </c>
-      <c r="J36" s="13" t="n">
+      <c r="K36" s="13" t="n">
         <v>14560</v>
       </c>
-      <c r="K36" s="13" t="n">
+      <c r="L36" s="13" t="n">
         <v>160</v>
       </c>
-      <c r="L36" s="14" t="n">
+      <c r="M36" s="14" t="n">
         <v>0.1334</v>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>35</v>
       </c>
@@ -2778,46 +2992,51 @@
           <t>@nirobrothers</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C37" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
           <t>Nirvaan and Vedant</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="F37" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="H37" s="13" t="n">
         <v>96835</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="I37" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I37" s="13" t="n">
+      <c r="J37" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="J37" s="13" t="n">
+      <c r="K37" s="13" t="n">
         <v>7841</v>
       </c>
-      <c r="K37" s="13" t="n">
+      <c r="L37" s="13" t="n">
         <v>116</v>
       </c>
-      <c r="L37" s="14" t="n">
+      <c r="M37" s="14" t="n">
         <v>0.08220000000000001</v>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="21" customHeight="1">
       <c r="A38" s="3" t="n">
         <v>36</v>
       </c>
@@ -2826,46 +3045,51 @@
           <t>@experiencebroadway_</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C38" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
           <t>Broadway</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F38" s="21" t="inlineStr">
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="H38" s="13" t="n">
         <v>95018</v>
       </c>
-      <c r="H38" s="13" t="n">
+      <c r="I38" s="13" t="n">
         <v>116</v>
       </c>
-      <c r="I38" s="13" t="n">
+      <c r="J38" s="13" t="n">
         <v>783</v>
       </c>
-      <c r="J38" s="13" t="n">
+      <c r="K38" s="13" t="n">
         <v>598</v>
       </c>
-      <c r="K38" s="13" t="n">
+      <c r="L38" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="L38" s="14" t="n">
+      <c r="M38" s="14" t="n">
         <v>0.006500000000000001</v>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
+    <row r="39" ht="21" customHeight="1">
       <c r="A39" s="3" t="n">
         <v>37</v>
       </c>
@@ -2874,46 +3098,51 @@
           <t>@nirvainnn</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C39" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
           <t>Nirvain</t>
         </is>
       </c>
-      <c r="E39" s="22" t="inlineStr">
+      <c r="F39" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>82093</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="I39" s="13" t="n">
         <v>336</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="J39" s="13" t="n">
         <v>362</v>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="K39" s="13" t="n">
         <v>6270</v>
       </c>
-      <c r="K39" s="13" t="n">
+      <c r="L39" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="L39" s="14" t="n">
+      <c r="M39" s="14" t="n">
         <v>0.077</v>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40" ht="21" customHeight="1">
       <c r="A40" s="3" t="n">
         <v>38</v>
       </c>
@@ -2922,46 +3151,51 @@
           <t>@ex_dee_anas</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C40" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
           <t>Md Anas</t>
         </is>
       </c>
-      <c r="E40" s="22" t="inlineStr">
+      <c r="F40" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F40" s="21" t="inlineStr">
+      <c r="G40" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="H40" s="13" t="n">
         <v>76988</v>
       </c>
-      <c r="H40" s="13" t="n">
+      <c r="I40" s="13" t="n">
         <v>5106</v>
       </c>
-      <c r="I40" s="13" t="n">
+      <c r="J40" s="13" t="n">
         <v>821</v>
       </c>
-      <c r="J40" s="13" t="n">
+      <c r="K40" s="13" t="n">
         <v>1738</v>
       </c>
-      <c r="K40" s="13" t="n">
+      <c r="L40" s="13" t="n">
         <v>32</v>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="M40" s="14" t="n">
         <v>0.023</v>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="21" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>39</v>
       </c>
@@ -2970,46 +3204,51 @@
           <t>@farakwear</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>FARAK | फरक</t>
         </is>
       </c>
-      <c r="E41" s="21" t="inlineStr">
+      <c r="F41" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="H41" s="13" t="n">
         <v>70746</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="I41" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="I41" s="13" t="n">
+      <c r="J41" s="13" t="n">
         <v>463</v>
       </c>
-      <c r="J41" s="13" t="n">
+      <c r="K41" s="13" t="n">
         <v>23278</v>
       </c>
-      <c r="K41" s="13" t="n">
+      <c r="L41" s="13" t="n">
         <v>178</v>
       </c>
-      <c r="L41" s="14" t="n">
+      <c r="M41" s="14" t="n">
         <v>0.3316</v>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="21" customHeight="1">
       <c r="A42" s="3" t="n">
         <v>40</v>
       </c>
@@ -3018,46 +3257,51 @@
           <t>@illuminatedmilk</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C42" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
           <t>Shachi</t>
         </is>
       </c>
-      <c r="E42" s="21" t="inlineStr">
+      <c r="F42" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F42" s="21" t="inlineStr">
+      <c r="G42" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>63655</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>2680</v>
       </c>
-      <c r="I42" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>358</v>
       </c>
-      <c r="J42" s="13" t="n">
+      <c r="K42" s="13" t="n">
         <v>2046</v>
       </c>
-      <c r="K42" s="13" t="n">
+      <c r="L42" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="L42" s="14" t="n">
+      <c r="M42" s="14" t="n">
         <v>0.0332</v>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43" ht="21" customHeight="1">
       <c r="A43" s="3" t="n">
         <v>41</v>
       </c>
@@ -3066,46 +3310,51 @@
           <t>@harshiitarora</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C43" s="53" t="inlineStr">
+        <is>
+          <t>✨ Mid-Tier Creator (50K - 100K)</t>
         </is>
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
           <t>Harshit Arora</t>
         </is>
       </c>
-      <c r="E43" s="21" t="inlineStr">
+      <c r="F43" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>55628</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="I43" s="13" t="n">
         <v>1140</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="J43" s="13" t="n">
         <v>649</v>
       </c>
-      <c r="J43" s="13" t="n">
+      <c r="K43" s="13" t="n">
         <v>254798</v>
       </c>
-      <c r="K43" s="13" t="n">
+      <c r="L43" s="13" t="n">
         <v>2153</v>
       </c>
-      <c r="L43" s="14" t="n">
+      <c r="M43" s="14" t="n">
         <v>4.6191</v>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44" ht="21" customHeight="1">
       <c r="A44" s="3" t="n">
         <v>42</v>
       </c>
@@ -3114,46 +3363,51 @@
           <t>@negiraman</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C44" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
           <t>Raman Negi</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
+      <c r="F44" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F44" s="21" t="inlineStr">
+      <c r="G44" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="H44" s="13" t="n">
         <v>47009</v>
       </c>
-      <c r="H44" s="13" t="n">
+      <c r="I44" s="13" t="n">
         <v>1834</v>
       </c>
-      <c r="I44" s="13" t="n">
+      <c r="J44" s="13" t="n">
         <v>193</v>
       </c>
-      <c r="J44" s="13" t="n">
+      <c r="K44" s="13" t="n">
         <v>912</v>
       </c>
-      <c r="K44" s="13" t="n">
+      <c r="L44" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="L44" s="14" t="n">
+      <c r="M44" s="14" t="n">
         <v>0.0199</v>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="21" customHeight="1">
       <c r="A45" s="3" t="n">
         <v>43</v>
       </c>
@@ -3162,46 +3416,51 @@
           <t>@talesofcityofficial</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C45" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
           <t>Tales of City ™</t>
         </is>
       </c>
-      <c r="E45" s="21" t="inlineStr">
+      <c r="F45" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F45" s="21" t="inlineStr">
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>44037</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="I45" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="I45" s="13" t="n">
+      <c r="J45" s="13" t="n">
         <v>540</v>
       </c>
-      <c r="J45" s="13" t="n">
+      <c r="K45" s="13" t="n">
         <v>2686</v>
       </c>
-      <c r="K45" s="13" t="n">
+      <c r="L45" s="13" t="n">
         <v>163</v>
       </c>
-      <c r="L45" s="14" t="n">
+      <c r="M45" s="14" t="n">
         <v>0.06469999999999999</v>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="21" customHeight="1">
       <c r="A46" s="3" t="n">
         <v>44</v>
       </c>
@@ -3210,46 +3469,51 @@
           <t>@nick.shayden</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C46" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
           <t>Nishchaiy Kamra</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
+      <c r="F46" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F46" s="21" t="inlineStr">
+      <c r="G46" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>40713</v>
       </c>
-      <c r="H46" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>997</v>
       </c>
-      <c r="I46" s="13" t="n">
+      <c r="J46" s="13" t="n">
         <v>341</v>
       </c>
-      <c r="J46" s="13" t="n">
+      <c r="K46" s="13" t="n">
         <v>2462</v>
       </c>
-      <c r="K46" s="13" t="n">
+      <c r="L46" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="L46" s="14" t="n">
+      <c r="M46" s="14" t="n">
         <v>0.0608</v>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="21" customHeight="1">
       <c r="A47" s="3" t="n">
         <v>45</v>
       </c>
@@ -3258,46 +3522,51 @@
           <t>@adityab27</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>Comet, Gully Labs</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>Aditya Bhalla</t>
         </is>
       </c>
-      <c r="E47" s="21" t="inlineStr">
+      <c r="F47" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F47" s="21" t="inlineStr">
+      <c r="G47" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="H47" s="13" t="n">
         <v>40490</v>
       </c>
-      <c r="H47" s="13" t="n">
+      <c r="I47" s="13" t="n">
         <v>1183</v>
       </c>
-      <c r="I47" s="13" t="n">
+      <c r="J47" s="13" t="n">
         <v>828</v>
       </c>
-      <c r="J47" s="13" t="n">
+      <c r="K47" s="13" t="n">
         <v>4895</v>
       </c>
-      <c r="K47" s="13" t="n">
+      <c r="L47" s="13" t="n">
         <v>97</v>
       </c>
-      <c r="L47" s="14" t="n">
+      <c r="M47" s="14" t="n">
         <v>0.1233</v>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48" ht="21" customHeight="1">
       <c r="A48" s="3" t="n">
         <v>46</v>
       </c>
@@ -3306,46 +3575,51 @@
           <t>@veronicasbombay</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Veronica’s</t>
         </is>
       </c>
-      <c r="E48" s="22" t="inlineStr">
+      <c r="F48" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F48" s="21" t="inlineStr">
+      <c r="G48" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>39041</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="I48" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="J48" s="13" t="n">
         <v>707</v>
       </c>
-      <c r="J48" s="13" t="n">
+      <c r="K48" s="13" t="n">
         <v>6645</v>
       </c>
-      <c r="K48" s="13" t="n">
+      <c r="L48" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="L48" s="14" t="n">
+      <c r="M48" s="14" t="n">
         <v>0.1721</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="21" customHeight="1">
       <c r="A49" s="3" t="n">
         <v>47</v>
       </c>
@@ -3354,46 +3628,51 @@
           <t>@sooka.mag</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C49" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
           <t>SOOKA</t>
         </is>
       </c>
-      <c r="E49" s="22" t="inlineStr">
+      <c r="F49" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F49" s="21" t="inlineStr">
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="H49" s="13" t="n">
         <v>38093</v>
       </c>
-      <c r="H49" s="13" t="n">
+      <c r="I49" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="I49" s="13" t="n">
+      <c r="J49" s="13" t="n">
         <v>402</v>
       </c>
-      <c r="J49" s="13" t="n">
+      <c r="K49" s="13" t="n">
         <v>42061</v>
       </c>
-      <c r="K49" s="13" t="n">
+      <c r="L49" s="13" t="n">
         <v>138</v>
       </c>
-      <c r="L49" s="14" t="n">
+      <c r="M49" s="14" t="n">
         <v>1.1078</v>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="21" customHeight="1">
       <c r="A50" s="3" t="n">
         <v>48</v>
       </c>
@@ -3402,46 +3681,51 @@
           <t>@yashvi.bhaia</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C50" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="inlineStr">
+        <is>
           <t>yashvi bhaia</t>
         </is>
       </c>
-      <c r="E50" s="22" t="inlineStr">
+      <c r="F50" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F50" s="21" t="inlineStr">
+      <c r="G50" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>32650</v>
       </c>
-      <c r="H50" s="13" t="n">
+      <c r="I50" s="13" t="n">
         <v>1270</v>
       </c>
-      <c r="I50" s="13" t="n">
+      <c r="J50" s="13" t="n">
         <v>265</v>
       </c>
-      <c r="J50" s="13" t="n">
+      <c r="K50" s="13" t="n">
         <v>5999</v>
       </c>
-      <c r="K50" s="13" t="n">
+      <c r="L50" s="13" t="n">
         <v>96</v>
       </c>
-      <c r="L50" s="14" t="n">
+      <c r="M50" s="14" t="n">
         <v>0.1867</v>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51" ht="21" customHeight="1">
       <c r="A51" s="3" t="n">
         <v>49</v>
       </c>
@@ -3450,46 +3734,51 @@
           <t>@vagavoom</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C51" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="inlineStr">
+        <is>
           <t>Vani Verma</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="F51" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F51" s="21" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>30734</v>
       </c>
-      <c r="H51" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>3141</v>
       </c>
-      <c r="I51" s="13" t="n">
+      <c r="J51" s="13" t="n">
         <v>1652</v>
       </c>
-      <c r="J51" s="13" t="n">
+      <c r="K51" s="13" t="n">
         <v>1423</v>
       </c>
-      <c r="K51" s="13" t="n">
+      <c r="L51" s="13" t="n">
         <v>36</v>
       </c>
-      <c r="L51" s="14" t="n">
+      <c r="M51" s="14" t="n">
         <v>0.0475</v>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="21" customHeight="1">
       <c r="A52" s="3" t="n">
         <v>50</v>
       </c>
@@ -3498,46 +3787,51 @@
           <t>@odd.noteven</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D52" s="15" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Odd Not Even</t>
         </is>
       </c>
-      <c r="E52" s="21" t="inlineStr">
+      <c r="F52" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F52" s="21" t="inlineStr">
+      <c r="G52" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G52" s="13" t="n">
+      <c r="H52" s="13" t="n">
         <v>26563</v>
       </c>
-      <c r="H52" s="13" t="n">
+      <c r="I52" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I52" s="13" t="n">
+      <c r="J52" s="13" t="n">
         <v>106</v>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="K52" s="13" t="n">
         <v>4942</v>
       </c>
-      <c r="K52" s="13" t="n">
+      <c r="L52" s="13" t="n">
         <v>77</v>
       </c>
-      <c r="L52" s="14" t="n">
+      <c r="M52" s="14" t="n">
         <v>0.1889</v>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="21" customHeight="1">
       <c r="A53" s="3" t="n">
         <v>51</v>
       </c>
@@ -3546,46 +3840,51 @@
           <t>@itspalakandmahir</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C53" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
           <t>Palak &amp; Mahir</t>
         </is>
       </c>
-      <c r="E53" s="22" t="inlineStr">
+      <c r="F53" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="H53" s="13" t="n">
         <v>23571</v>
       </c>
-      <c r="H53" s="13" t="n">
+      <c r="I53" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="I53" s="13" t="n">
+      <c r="J53" s="13" t="n">
         <v>220</v>
       </c>
-      <c r="J53" s="13" t="n">
+      <c r="K53" s="13" t="n">
         <v>1781</v>
       </c>
-      <c r="K53" s="13" t="n">
+      <c r="L53" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="L53" s="14" t="n">
+      <c r="M53" s="14" t="n">
         <v>0.07580000000000001</v>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="21" customHeight="1">
       <c r="A54" s="3" t="n">
         <v>52</v>
       </c>
@@ -3594,46 +3893,51 @@
           <t>@ghar.1964</t>
         </is>
       </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C54" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
           <t>GHAR 1964 | Stay &amp; cafe | Sojha | Himachal📍</t>
         </is>
       </c>
-      <c r="E54" s="22" t="inlineStr">
+      <c r="F54" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="G54" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G54" s="13" t="n">
+      <c r="H54" s="13" t="n">
         <v>22188</v>
       </c>
-      <c r="H54" s="13" t="n">
+      <c r="I54" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="I54" s="13" t="n">
+      <c r="J54" s="13" t="n">
         <v>423</v>
       </c>
-      <c r="J54" s="13" t="n">
+      <c r="K54" s="13" t="n">
         <v>6547</v>
       </c>
-      <c r="K54" s="13" t="n">
+      <c r="L54" s="13" t="n">
         <v>101</v>
       </c>
-      <c r="L54" s="14" t="n">
+      <c r="M54" s="14" t="n">
         <v>0.2996</v>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55" ht="21" customHeight="1">
       <c r="A55" s="3" t="n">
         <v>53</v>
       </c>
@@ -3642,46 +3946,51 @@
           <t>@eternalramblings</t>
         </is>
       </c>
-      <c r="C55" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C55" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
           <t>Mayank Mittal | KAPOW! | EternalRamblings</t>
         </is>
       </c>
-      <c r="E55" s="22" t="inlineStr">
+      <c r="F55" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="G55" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="H55" s="13" t="n">
         <v>20485</v>
       </c>
-      <c r="H55" s="13" t="n">
+      <c r="I55" s="13" t="n">
         <v>2343</v>
       </c>
-      <c r="I55" s="13" t="n">
+      <c r="J55" s="13" t="n">
         <v>477</v>
       </c>
-      <c r="J55" s="13" t="n">
+      <c r="K55" s="13" t="n">
         <v>421</v>
       </c>
-      <c r="K55" s="13" t="n">
+      <c r="L55" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="L55" s="14" t="n">
+      <c r="M55" s="14" t="n">
         <v>0.0226</v>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="21" customHeight="1">
       <c r="A56" s="3" t="n">
         <v>54</v>
       </c>
@@ -3690,46 +3999,51 @@
           <t>@kevalnova</t>
         </is>
       </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C56" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
           <t>Keval Patel</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="G56" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G56" s="13" t="n">
+      <c r="H56" s="13" t="n">
         <v>19340</v>
       </c>
-      <c r="H56" s="13" t="n">
+      <c r="I56" s="13" t="n">
         <v>264</v>
       </c>
-      <c r="I56" s="13" t="n">
+      <c r="J56" s="13" t="n">
         <v>214</v>
       </c>
-      <c r="J56" s="13" t="n">
+      <c r="K56" s="13" t="n">
         <v>2284</v>
       </c>
-      <c r="K56" s="13" t="n">
+      <c r="L56" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="L56" s="14" t="n">
+      <c r="M56" s="14" t="n">
         <v>0.1207</v>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
+    <row r="57" ht="21" customHeight="1">
       <c r="A57" s="3" t="n">
         <v>55</v>
       </c>
@@ -3738,46 +4052,51 @@
           <t>@jhillmildhoot</t>
         </is>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="C57" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>jhillmildhoot</t>
         </is>
       </c>
-      <c r="E57" s="22" t="inlineStr">
+      <c r="F57" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F57" s="21" t="inlineStr">
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="H57" s="13" t="n">
         <v>18950</v>
       </c>
-      <c r="H57" s="13" t="n">
+      <c r="I57" s="13" t="n">
         <v>754</v>
       </c>
-      <c r="I57" s="13" t="n">
+      <c r="J57" s="13" t="n">
         <v>199</v>
       </c>
-      <c r="J57" s="13" t="n">
+      <c r="K57" s="13" t="n">
         <v>1457</v>
       </c>
-      <c r="K57" s="13" t="n">
+      <c r="L57" s="13" t="n">
         <v>48</v>
       </c>
-      <c r="L57" s="14" t="n">
+      <c r="M57" s="14" t="n">
         <v>0.0794</v>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="21" customHeight="1">
       <c r="A58" s="3" t="n">
         <v>56</v>
       </c>
@@ -3786,46 +4105,51 @@
           <t>@akshay_freestyle</t>
         </is>
       </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C58" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
           <t>Akshay Yadav |Football Freestyle</t>
         </is>
       </c>
-      <c r="E58" s="22" t="inlineStr">
+      <c r="F58" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F58" s="21" t="inlineStr">
+      <c r="G58" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G58" s="13" t="n">
+      <c r="H58" s="13" t="n">
         <v>17820</v>
       </c>
-      <c r="H58" s="13" t="n">
+      <c r="I58" s="13" t="n">
         <v>1366</v>
       </c>
-      <c r="I58" s="13" t="n">
+      <c r="J58" s="13" t="n">
         <v>1045</v>
       </c>
-      <c r="J58" s="13" t="n">
+      <c r="K58" s="13" t="n">
         <v>591</v>
       </c>
-      <c r="K58" s="13" t="n">
+      <c r="L58" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="L58" s="14" t="n">
+      <c r="M58" s="14" t="n">
         <v>0.0355</v>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="21" customHeight="1">
       <c r="A59" s="3" t="n">
         <v>57</v>
       </c>
@@ -3834,46 +4158,51 @@
           <t>@gullylabs.global</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C59" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
           <t>gullylabs.global</t>
         </is>
       </c>
-      <c r="E59" s="22" t="inlineStr">
+      <c r="F59" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F59" s="21" t="inlineStr">
+      <c r="G59" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G59" s="13" t="n">
+      <c r="H59" s="13" t="n">
         <v>17077</v>
       </c>
-      <c r="H59" s="13" t="n">
+      <c r="I59" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="I59" s="13" t="n">
+      <c r="J59" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="J59" s="13" t="n">
+      <c r="K59" s="13" t="n">
         <v>1648</v>
       </c>
-      <c r="K59" s="13" t="n">
+      <c r="L59" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="L59" s="14" t="n">
+      <c r="M59" s="14" t="n">
         <v>0.0977</v>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="21" customHeight="1">
       <c r="A60" s="3" t="n">
         <v>58</v>
       </c>
@@ -3882,46 +4211,51 @@
           <t>@itskapowtime</t>
         </is>
       </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C60" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
           <t>KAPOW! (कपाओ!) 💣</t>
         </is>
       </c>
-      <c r="E60" s="21" t="inlineStr">
+      <c r="F60" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F60" s="21" t="inlineStr">
+      <c r="G60" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G60" s="13" t="n">
+      <c r="H60" s="13" t="n">
         <v>15262</v>
       </c>
-      <c r="H60" s="13" t="n">
+      <c r="I60" s="13" t="n">
         <v>284</v>
       </c>
-      <c r="I60" s="13" t="n">
+      <c r="J60" s="13" t="n">
         <v>659</v>
       </c>
-      <c r="J60" s="13" t="n">
+      <c r="K60" s="13" t="n">
         <v>2148</v>
       </c>
-      <c r="K60" s="13" t="n">
+      <c r="L60" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="L60" s="14" t="n">
+      <c r="M60" s="14" t="n">
         <v>0.1418</v>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="21" customHeight="1">
       <c r="A61" s="3" t="n">
         <v>59</v>
       </c>
@@ -3930,46 +4264,51 @@
           <t>@saffaaah</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C61" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
           <t>saffah👼🏽 | presenter &amp; content creator</t>
         </is>
       </c>
-      <c r="E61" s="22" t="inlineStr">
+      <c r="F61" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F61" s="21" t="inlineStr">
+      <c r="G61" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G61" s="13" t="n">
+      <c r="H61" s="13" t="n">
         <v>11927</v>
       </c>
-      <c r="H61" s="13" t="n">
+      <c r="I61" s="13" t="n">
         <v>4043</v>
       </c>
-      <c r="I61" s="13" t="n">
+      <c r="J61" s="13" t="n">
         <v>132</v>
       </c>
-      <c r="J61" s="13" t="n">
+      <c r="K61" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="K61" s="13" t="n">
+      <c r="L61" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="L61" s="14" t="n">
+      <c r="M61" s="14" t="n">
         <v>0.0019</v>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="21" customHeight="1">
       <c r="A62" s="3" t="n">
         <v>60</v>
       </c>
@@ -3978,46 +4317,51 @@
           <t>@dominasianmagazine</t>
         </is>
       </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C62" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
           <t>DominAsian Magazine</t>
         </is>
       </c>
-      <c r="E62" s="22" t="inlineStr">
+      <c r="F62" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F62" s="21" t="inlineStr">
+      <c r="G62" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G62" s="13" t="n">
+      <c r="H62" s="13" t="n">
         <v>10868</v>
       </c>
-      <c r="H62" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>1971</v>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>470</v>
       </c>
-      <c r="J62" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>567</v>
       </c>
-      <c r="K62" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="L62" s="14" t="n">
+      <c r="M62" s="14" t="n">
         <v>0.0532</v>
       </c>
     </row>
-    <row r="63" ht="20" customHeight="1">
+    <row r="63" ht="21" customHeight="1">
       <c r="A63" s="3" t="n">
         <v>61</v>
       </c>
@@ -4026,46 +4370,51 @@
           <t>@lambo.drive</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C63" s="54" t="inlineStr">
+        <is>
+          <t>🎯 Micro Creator (10K - 50K)</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
           <t>Janesh Arya</t>
         </is>
       </c>
-      <c r="E63" s="21" t="inlineStr">
+      <c r="F63" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F63" s="21" t="inlineStr">
+      <c r="G63" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G63" s="13" t="n">
+      <c r="H63" s="13" t="n">
         <v>10604</v>
       </c>
-      <c r="H63" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>5036</v>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="J63" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="K63" s="13" t="n">
         <v>1815</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="L63" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="L63" s="14" t="n">
+      <c r="M63" s="14" t="n">
         <v>0.1796</v>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
+    <row r="64" ht="21" customHeight="1">
       <c r="A64" s="3" t="n">
         <v>62</v>
       </c>
@@ -4074,46 +4423,51 @@
           <t>@thecometnucleus</t>
         </is>
       </c>
-      <c r="C64" s="15" t="inlineStr">
+      <c r="C64" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="E64" s="15" t="inlineStr">
         <is>
           <t>Comet Nucleus</t>
         </is>
       </c>
-      <c r="E64" s="22" t="inlineStr">
+      <c r="F64" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F64" s="21" t="inlineStr">
+      <c r="G64" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G64" s="13" t="n">
+      <c r="H64" s="13" t="n">
         <v>8495</v>
       </c>
-      <c r="H64" s="13" t="n">
+      <c r="I64" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="13" t="n">
+      <c r="J64" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="J64" s="13" t="n">
+      <c r="K64" s="13" t="n">
         <v>5534</v>
       </c>
-      <c r="K64" s="13" t="n">
+      <c r="L64" s="13" t="n">
         <v>73</v>
       </c>
-      <c r="L64" s="14" t="n">
+      <c r="M64" s="14" t="n">
         <v>0.66</v>
       </c>
     </row>
-    <row r="65" ht="20" customHeight="1">
+    <row r="65" ht="21" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>63</v>
       </c>
@@ -4122,46 +4476,51 @@
           <t>@snkrhood.in</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C65" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
           <t>SNKRHOOD</t>
         </is>
       </c>
-      <c r="E65" s="22" t="inlineStr">
+      <c r="F65" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F65" s="21" t="inlineStr">
+      <c r="G65" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G65" s="13" t="n">
+      <c r="H65" s="13" t="n">
         <v>6325</v>
       </c>
-      <c r="H65" s="13" t="n">
+      <c r="I65" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="J65" s="13" t="n">
         <v>211</v>
       </c>
-      <c r="J65" s="13" t="n">
+      <c r="K65" s="13" t="n">
         <v>675</v>
       </c>
-      <c r="K65" s="13" t="n">
+      <c r="L65" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="L65" s="14" t="n">
+      <c r="M65" s="14" t="n">
         <v>0.1075</v>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
+    <row r="66" ht="21" customHeight="1">
       <c r="A66" s="3" t="n">
         <v>64</v>
       </c>
@@ -4170,46 +4529,51 @@
           <t>@ukato.music</t>
         </is>
       </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C66" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
           <t>UKato | Utkarsh Singh</t>
         </is>
       </c>
-      <c r="E66" s="22" t="inlineStr">
+      <c r="F66" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F66" s="21" t="inlineStr">
+      <c r="G66" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G66" s="13" t="n">
+      <c r="H66" s="13" t="n">
         <v>5546</v>
       </c>
-      <c r="H66" s="13" t="n">
+      <c r="I66" s="13" t="n">
         <v>1985</v>
       </c>
-      <c r="I66" s="13" t="n">
+      <c r="J66" s="13" t="n">
         <v>81</v>
       </c>
-      <c r="J66" s="13" t="n">
+      <c r="K66" s="13" t="n">
         <v>1590</v>
       </c>
-      <c r="K66" s="13" t="n">
+      <c r="L66" s="13" t="n">
         <v>43</v>
       </c>
-      <c r="L66" s="14" t="n">
+      <c r="M66" s="14" t="n">
         <v>0.2944</v>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
+    <row r="67" ht="21" customHeight="1">
       <c r="A67" s="3" t="n">
         <v>65</v>
       </c>
@@ -4218,46 +4582,51 @@
           <t>@delhiartweekend</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
           <t>Delhi Art Weekend</t>
         </is>
       </c>
-      <c r="E67" s="21" t="inlineStr">
+      <c r="F67" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F67" s="21" t="inlineStr">
+      <c r="G67" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G67" s="13" t="n">
+      <c r="H67" s="13" t="n">
         <v>4419</v>
       </c>
-      <c r="H67" s="13" t="n">
+      <c r="I67" s="13" t="n">
         <v>41</v>
       </c>
-      <c r="I67" s="13" t="n">
+      <c r="J67" s="13" t="n">
         <v>146</v>
       </c>
-      <c r="J67" s="13" t="n">
+      <c r="K67" s="13" t="n">
         <v>103</v>
       </c>
-      <c r="K67" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="14" t="n">
+      <c r="L67" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="14" t="n">
         <v>0.0233</v>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
+    <row r="68" ht="21" customHeight="1">
       <c r="A68" s="3" t="n">
         <v>66</v>
       </c>
@@ -4266,46 +4635,51 @@
           <t>@amra.ldn</t>
         </is>
       </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C68" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
           <t>AMRA</t>
         </is>
       </c>
-      <c r="E68" s="22" t="inlineStr">
+      <c r="F68" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F68" s="21" t="inlineStr">
+      <c r="G68" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G68" s="13" t="n">
+      <c r="H68" s="13" t="n">
         <v>3966</v>
       </c>
-      <c r="H68" s="13" t="n">
+      <c r="I68" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I68" s="13" t="n">
+      <c r="J68" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="K68" s="13" t="n">
         <v>509</v>
       </c>
-      <c r="K68" s="13" t="n">
+      <c r="L68" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="L68" s="14" t="n">
+      <c r="M68" s="14" t="n">
         <v>0.1324</v>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
+    <row r="69" ht="21" customHeight="1">
       <c r="A69" s="3" t="n">
         <v>67</v>
       </c>
@@ -4314,46 +4688,51 @@
           <t>@gurshaabedi</t>
         </is>
       </c>
-      <c r="C69" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C69" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
           <t>Gurshaa</t>
         </is>
       </c>
-      <c r="E69" s="22" t="inlineStr">
+      <c r="F69" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F69" s="21" t="inlineStr">
+      <c r="G69" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G69" s="13" t="n">
+      <c r="H69" s="13" t="n">
         <v>3788</v>
       </c>
-      <c r="H69" s="13" t="n">
+      <c r="I69" s="13" t="n">
         <v>3399</v>
       </c>
-      <c r="I69" s="13" t="n">
+      <c r="J69" s="13" t="n">
         <v>447</v>
       </c>
-      <c r="J69" s="13" t="n">
+      <c r="K69" s="13" t="n">
         <v>2074</v>
       </c>
-      <c r="K69" s="13" t="n">
+      <c r="L69" s="13" t="n">
         <v>108</v>
       </c>
-      <c r="L69" s="14" t="n">
+      <c r="M69" s="14" t="n">
         <v>0.5760000000000001</v>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
+    <row r="70" ht="21" customHeight="1">
       <c r="A70" s="3" t="n">
         <v>68</v>
       </c>
@@ -4362,46 +4741,51 @@
           <t>@utkgpt</t>
         </is>
       </c>
-      <c r="C70" s="15" t="inlineStr">
+      <c r="C70" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="E70" s="15" t="inlineStr">
         <is>
           <t>Utkarsh Gupta</t>
         </is>
       </c>
-      <c r="E70" s="21" t="inlineStr">
+      <c r="F70" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F70" s="22" t="inlineStr">
+      <c r="G70" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G70" s="13" t="n">
+      <c r="H70" s="13" t="n">
         <v>3051</v>
       </c>
-      <c r="H70" s="13" t="n">
+      <c r="I70" s="13" t="n">
         <v>1262</v>
       </c>
-      <c r="I70" s="13" t="n">
+      <c r="J70" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="J70" s="13" t="n">
+      <c r="K70" s="13" t="n">
         <v>8079</v>
       </c>
-      <c r="K70" s="13" t="n">
+      <c r="L70" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="L70" s="14" t="n">
+      <c r="M70" s="14" t="n">
         <v>2.6873</v>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
+    <row r="71" ht="21" customHeight="1">
       <c r="A71" s="3" t="n">
         <v>69</v>
       </c>
@@ -4410,46 +4794,51 @@
           <t>@norbu.noises</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C71" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D71" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
           <t>Norbu</t>
         </is>
       </c>
-      <c r="E71" s="22" t="inlineStr">
+      <c r="F71" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F71" s="21" t="inlineStr">
+      <c r="G71" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G71" s="13" t="n">
+      <c r="H71" s="13" t="n">
         <v>1980</v>
       </c>
-      <c r="H71" s="13" t="n">
+      <c r="I71" s="13" t="n">
         <v>999</v>
       </c>
-      <c r="I71" s="13" t="n">
+      <c r="J71" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="J71" s="13" t="n">
+      <c r="K71" s="13" t="n">
         <v>448</v>
       </c>
-      <c r="K71" s="13" t="n">
+      <c r="L71" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L71" s="14" t="n">
+      <c r="M71" s="14" t="n">
         <v>0.2303</v>
       </c>
     </row>
-    <row r="72" ht="20" customHeight="1">
+    <row r="72" ht="21" customHeight="1">
       <c r="A72" s="3" t="n">
         <v>70</v>
       </c>
@@ -4458,46 +4847,51 @@
           <t>@ofthewilderness.otw</t>
         </is>
       </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C72" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
           <t>Of the Wilderness</t>
         </is>
       </c>
-      <c r="E72" s="22" t="inlineStr">
+      <c r="F72" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F72" s="21" t="inlineStr">
+      <c r="G72" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G72" s="13" t="n">
+      <c r="H72" s="13" t="n">
         <v>857</v>
       </c>
-      <c r="H72" s="13" t="n">
+      <c r="I72" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="I72" s="13" t="n">
+      <c r="J72" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="J72" s="13" t="n">
+      <c r="K72" s="13" t="n">
         <v>50223</v>
       </c>
-      <c r="K72" s="13" t="n">
+      <c r="L72" s="13" t="n">
         <v>273</v>
       </c>
-      <c r="L72" s="14" t="n">
+      <c r="M72" s="14" t="n">
         <v>58.9218</v>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
+    <row r="73" ht="21" customHeight="1">
       <c r="A73" s="3" t="n">
         <v>71</v>
       </c>
@@ -4506,46 +4900,51 @@
           <t>@quatre.creators</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C73" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
           <t>Quatre</t>
         </is>
       </c>
-      <c r="E73" s="22" t="inlineStr">
+      <c r="F73" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F73" s="21" t="inlineStr">
+      <c r="G73" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G73" s="13" t="n">
+      <c r="H73" s="13" t="n">
         <v>417</v>
       </c>
-      <c r="H73" s="13" t="n">
+      <c r="I73" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I73" s="13" t="n">
+      <c r="J73" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="J73" s="13" t="n">
+      <c r="K73" s="13" t="n">
         <v>356</v>
       </c>
-      <c r="K73" s="13" t="n">
+      <c r="L73" s="13" t="n">
         <v>63</v>
       </c>
-      <c r="L73" s="14" t="n">
+      <c r="M73" s="14" t="n">
         <v>1.0048</v>
       </c>
     </row>
-    <row r="74" ht="20" customHeight="1">
+    <row r="74" ht="21" customHeight="1">
       <c r="A74" s="3" t="n">
         <v>72</v>
       </c>
@@ -4554,29 +4953,31 @@
           <t>@capsulindia</t>
         </is>
       </c>
-      <c r="C74" s="15" t="inlineStr">
+      <c r="C74" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D74" s="15" t="inlineStr">
+      <c r="E74" s="15" t="inlineStr">
         <is>
           <t>CAPSUL</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
+      <c r="F74" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F74" s="22" t="inlineStr">
+      <c r="G74" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G74" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" s="13" t="n">
         <v>0</v>
       </c>
@@ -4584,16 +4985,19 @@
         <v>0</v>
       </c>
       <c r="J74" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="13" t="n">
         <v>2276</v>
       </c>
-      <c r="K74" s="13" t="n">
+      <c r="L74" s="13" t="n">
         <v>37</v>
       </c>
-      <c r="L74" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
+      <c r="M74" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="21" customHeight="1">
       <c r="A75" s="3" t="n">
         <v>73</v>
       </c>
@@ -4602,29 +5006,31 @@
           <t>@amazonfashionin</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C75" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
           <t>Amazon Fashion India</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="F75" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F75" s="22" t="inlineStr">
+      <c r="G75" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G75" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H75" s="13" t="n">
         <v>0</v>
       </c>
@@ -4632,16 +5038,19 @@
         <v>0</v>
       </c>
       <c r="J75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="13" t="n">
         <v>421</v>
       </c>
-      <c r="K75" s="13" t="n">
+      <c r="L75" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="L75" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
+      <c r="M75" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="21" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>74</v>
       </c>
@@ -4650,29 +5059,31 @@
           <t>@bombaysweetshop</t>
         </is>
       </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C76" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
           <t>Bombay Sweet Shop</t>
         </is>
       </c>
-      <c r="E76" s="21" t="inlineStr">
+      <c r="F76" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F76" s="22" t="inlineStr">
+      <c r="G76" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G76" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H76" s="13" t="n">
         <v>0</v>
       </c>
@@ -4680,16 +5091,19 @@
         <v>0</v>
       </c>
       <c r="J76" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="13" t="n">
         <v>694</v>
       </c>
-      <c r="K76" s="13" t="n">
+      <c r="L76" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="L76" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1">
+      <c r="M76" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" ht="21" customHeight="1">
       <c r="A77" s="3" t="n">
         <v>75</v>
       </c>
@@ -4698,29 +5112,31 @@
           <t>@casabacardiin</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="C77" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>Casa Bacardi</t>
         </is>
       </c>
-      <c r="E77" s="22" t="inlineStr">
+      <c r="F77" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F77" s="22" t="inlineStr">
+      <c r="G77" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G77" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H77" s="13" t="n">
         <v>0</v>
       </c>
@@ -4728,16 +5144,19 @@
         <v>0</v>
       </c>
       <c r="J77" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="13" t="n">
         <v>8370</v>
       </c>
-      <c r="K77" s="13" t="n">
+      <c r="L77" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="L77" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1">
+      <c r="M77" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="21" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>76</v>
       </c>
@@ -4746,29 +5165,31 @@
           <t>@cmf.tech</t>
         </is>
       </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C78" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
           <t>CMF by Nothing</t>
         </is>
       </c>
-      <c r="E78" s="21" t="inlineStr">
+      <c r="F78" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F78" s="22" t="inlineStr">
+      <c r="G78" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G78" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H78" s="13" t="n">
         <v>0</v>
       </c>
@@ -4776,16 +5197,19 @@
         <v>0</v>
       </c>
       <c r="J78" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="13" t="n">
         <v>4529</v>
       </c>
-      <c r="K78" s="13" t="n">
+      <c r="L78" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="L78" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
+      <c r="M78" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="21" customHeight="1">
       <c r="A79" s="3" t="n">
         <v>77</v>
       </c>
@@ -4794,29 +5218,31 @@
           <t>@districtupdates</t>
         </is>
       </c>
-      <c r="C79" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C79" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
           <t>District Updates</t>
         </is>
       </c>
-      <c r="E79" s="21" t="inlineStr">
+      <c r="F79" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F79" s="22" t="inlineStr">
+      <c r="G79" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G79" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H79" s="13" t="n">
         <v>0</v>
       </c>
@@ -4824,16 +5250,19 @@
         <v>0</v>
       </c>
       <c r="J79" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="13" t="n">
         <v>511</v>
       </c>
-      <c r="K79" s="13" t="n">
+      <c r="L79" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L79" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="20" customHeight="1">
+      <c r="M79" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="21" customHeight="1">
       <c r="A80" s="3" t="n">
         <v>78</v>
       </c>
@@ -4842,29 +5271,31 @@
           <t>@evaxfried</t>
         </is>
       </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C80" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E80" s="15" t="inlineStr">
+        <is>
           <t>Eva Gurung🫧</t>
         </is>
       </c>
-      <c r="E80" s="22" t="inlineStr">
+      <c r="F80" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F80" s="22" t="inlineStr">
+      <c r="G80" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G80" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H80" s="13" t="n">
         <v>0</v>
       </c>
@@ -4872,16 +5303,19 @@
         <v>0</v>
       </c>
       <c r="J80" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="13" t="n">
         <v>805</v>
       </c>
-      <c r="K80" s="13" t="n">
+      <c r="L80" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="L80" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1">
+      <c r="M80" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" ht="21" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>79</v>
       </c>
@@ -4890,29 +5324,31 @@
           <t>@indiansneakerfestival</t>
         </is>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="C81" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>Comet</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="E81" s="15" t="inlineStr">
         <is>
           <t>Indian Sneaker Festival</t>
         </is>
       </c>
-      <c r="E81" s="21" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F81" s="22" t="inlineStr">
+      <c r="G81" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G81" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H81" s="13" t="n">
         <v>0</v>
       </c>
@@ -4920,16 +5356,19 @@
         <v>0</v>
       </c>
       <c r="J81" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="13" t="n">
         <v>1702</v>
       </c>
-      <c r="K81" s="13" t="n">
+      <c r="L81" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="L81" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="20" customHeight="1">
+      <c r="M81" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="21" customHeight="1">
       <c r="A82" s="3" t="n">
         <v>80</v>
       </c>
@@ -4938,29 +5377,31 @@
           <t>@kanchhiiii</t>
         </is>
       </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C82" s="55" t="inlineStr">
+        <is>
+          <t>🌱 Nano Creator (&lt;10K)</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E82" s="15" t="inlineStr">
+        <is>
           <t>Kanishk Anand</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
+      <c r="F82" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F82" s="22" t="inlineStr">
+      <c r="G82" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G82" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H82" s="13" t="n">
         <v>0</v>
       </c>
@@ -4968,16 +5409,19 @@
         <v>0</v>
       </c>
       <c r="J82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="13" t="n">
         <v>8133</v>
       </c>
-      <c r="K82" s="13" t="n">
+      <c r="L82" s="13" t="n">
         <v>31</v>
       </c>
-      <c r="L82" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
+      <c r="M82" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" ht="21" customHeight="1">
       <c r="A83" s="3" t="n">
         <v>81</v>
       </c>
@@ -4986,29 +5430,31 @@
           <t>@kommunedelhincr</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C83" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
           <t>Kommune Delhi-NCR</t>
         </is>
       </c>
-      <c r="E83" s="22" t="inlineStr">
+      <c r="F83" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F83" s="22" t="inlineStr">
+      <c r="G83" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G83" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H83" s="13" t="n">
         <v>0</v>
       </c>
@@ -5016,16 +5462,19 @@
         <v>0</v>
       </c>
       <c r="J83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="13" t="n">
         <v>910</v>
       </c>
-      <c r="K83" s="13" t="n">
+      <c r="L83" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="L83" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1">
+      <c r="M83" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="21" customHeight="1">
       <c r="A84" s="3" t="n">
         <v>82</v>
       </c>
@@ -5034,29 +5483,31 @@
           <t>@medusaindia</t>
         </is>
       </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C84" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E84" s="15" t="inlineStr">
+        <is>
           <t>Medusa</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="F84" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F84" s="22" t="inlineStr">
+      <c r="G84" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G84" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H84" s="13" t="n">
         <v>0</v>
       </c>
@@ -5064,16 +5515,19 @@
         <v>0</v>
       </c>
       <c r="J84" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="13" t="n">
         <v>439</v>
       </c>
-      <c r="K84" s="13" t="n">
+      <c r="L84" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="L84" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
+      <c r="M84" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
       <c r="A85" s="3" t="n">
         <v>83</v>
       </c>
@@ -5082,29 +5536,31 @@
           <t>@kauraverse</t>
         </is>
       </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C85" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
           <t>KAURAVERSE</t>
         </is>
       </c>
-      <c r="E85" s="22" t="inlineStr">
+      <c r="F85" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F85" s="22" t="inlineStr">
+      <c r="G85" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G85" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H85" s="13" t="n">
         <v>0</v>
       </c>
@@ -5112,16 +5568,19 @@
         <v>0</v>
       </c>
       <c r="J85" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="13" t="n">
         <v>10303</v>
       </c>
-      <c r="K85" s="13" t="n">
+      <c r="L85" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="L85" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1">
+      <c r="M85" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="21" customHeight="1">
       <c r="A86" s="3" t="n">
         <v>84</v>
       </c>
@@ -5130,29 +5589,31 @@
           <t>@leada.in</t>
         </is>
       </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C86" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E86" s="15" t="inlineStr">
+        <is>
           <t>LEAD-A</t>
         </is>
       </c>
-      <c r="E86" s="22" t="inlineStr">
+      <c r="F86" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F86" s="22" t="inlineStr">
+      <c r="G86" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G86" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H86" s="13" t="n">
         <v>0</v>
       </c>
@@ -5160,16 +5621,19 @@
         <v>0</v>
       </c>
       <c r="J86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="13" t="n">
         <v>5444</v>
       </c>
-      <c r="K86" s="13" t="n">
+      <c r="L86" s="13" t="n">
         <v>64</v>
       </c>
-      <c r="L86" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="20" customHeight="1">
+      <c r="M86" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="21" customHeight="1">
       <c r="A87" s="3" t="n">
         <v>85</v>
       </c>
@@ -5178,29 +5642,31 @@
           <t>@niviasports</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C87" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
           <t>Nivia Sports</t>
         </is>
       </c>
-      <c r="E87" s="21" t="inlineStr">
+      <c r="F87" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F87" s="22" t="inlineStr">
+      <c r="G87" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G87" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H87" s="13" t="n">
         <v>0</v>
       </c>
@@ -5208,16 +5674,19 @@
         <v>0</v>
       </c>
       <c r="J87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="13" t="n">
         <v>2579</v>
       </c>
-      <c r="K87" s="13" t="n">
+      <c r="L87" s="13" t="n">
         <v>45</v>
       </c>
-      <c r="L87" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1">
+      <c r="M87" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
       <c r="A88" s="3" t="n">
         <v>86</v>
       </c>
@@ -5226,29 +5695,31 @@
           <t>@myntra</t>
         </is>
       </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="C88" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D88" s="15" t="inlineStr">
         <is>
           <t>Comet, Gully Labs</t>
         </is>
       </c>
-      <c r="D88" s="15" t="inlineStr">
+      <c r="E88" s="15" t="inlineStr">
         <is>
           <t>MYNTRA</t>
         </is>
       </c>
-      <c r="E88" s="21" t="inlineStr">
+      <c r="F88" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F88" s="22" t="inlineStr">
+      <c r="G88" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G88" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H88" s="13" t="n">
         <v>0</v>
       </c>
@@ -5256,16 +5727,19 @@
         <v>0</v>
       </c>
       <c r="J88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="13" t="n">
         <v>4981</v>
       </c>
-      <c r="K88" s="13" t="n">
+      <c r="L88" s="13" t="n">
         <v>227</v>
       </c>
-      <c r="L88" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
+      <c r="M88" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
       <c r="A89" s="3" t="n">
         <v>87</v>
       </c>
@@ -5274,29 +5748,31 @@
           <t>@rahasyafragrances</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C89" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
           <t>Rahasya Fragrances</t>
         </is>
       </c>
-      <c r="E89" s="22" t="inlineStr">
+      <c r="F89" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F89" s="22" t="inlineStr">
+      <c r="G89" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G89" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H89" s="13" t="n">
         <v>0</v>
       </c>
@@ -5304,16 +5780,19 @@
         <v>0</v>
       </c>
       <c r="J89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="13" t="n">
         <v>3690</v>
       </c>
-      <c r="K89" s="13" t="n">
+      <c r="L89" s="13" t="n">
         <v>38</v>
       </c>
-      <c r="L89" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1">
+      <c r="M89" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
       <c r="A90" s="3" t="n">
         <v>88</v>
       </c>
@@ -5322,29 +5801,31 @@
           <t>@parvaazmusic</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C90" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
           <t>parvaaz</t>
         </is>
       </c>
-      <c r="E90" s="21" t="inlineStr">
+      <c r="F90" s="21" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="F90" s="22" t="inlineStr">
+      <c r="G90" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G90" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H90" s="13" t="n">
         <v>0</v>
       </c>
@@ -5352,16 +5833,19 @@
         <v>0</v>
       </c>
       <c r="J90" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13" t="n">
         <v>1515</v>
       </c>
-      <c r="K90" s="13" t="n">
+      <c r="L90" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="L90" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="20" customHeight="1">
+      <c r="M90" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
       <c r="A91" s="3" t="n">
         <v>89</v>
       </c>
@@ -5370,29 +5854,31 @@
           <t>@skecherscricket</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr">
+      <c r="C91" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>Skechers India</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
+      <c r="E91" s="15" t="inlineStr">
         <is>
           <t>Skechers Cricket</t>
         </is>
       </c>
-      <c r="E91" s="22" t="inlineStr">
+      <c r="F91" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F91" s="22" t="inlineStr">
+      <c r="G91" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G91" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H91" s="13" t="n">
         <v>0</v>
       </c>
@@ -5400,16 +5886,19 @@
         <v>0</v>
       </c>
       <c r="J91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="13" t="n">
         <v>450</v>
       </c>
-      <c r="K91" s="13" t="n">
+      <c r="L91" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="L91" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="20" customHeight="1">
+      <c r="M91" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="21" customHeight="1">
       <c r="A92" s="3" t="n">
         <v>90</v>
       </c>
@@ -5418,29 +5907,31 @@
           <t>@thethirdspacedelhi</t>
         </is>
       </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C92" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
           <t>Third Space</t>
         </is>
       </c>
-      <c r="E92" s="22" t="inlineStr">
+      <c r="F92" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F92" s="22" t="inlineStr">
+      <c r="G92" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G92" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H92" s="13" t="n">
         <v>0</v>
       </c>
@@ -5448,16 +5939,19 @@
         <v>0</v>
       </c>
       <c r="J92" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="13" t="n">
         <v>1339</v>
       </c>
-      <c r="K92" s="13" t="n">
+      <c r="L92" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="L92" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1">
+      <c r="M92" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
       <c r="A93" s="3" t="n">
         <v>91</v>
       </c>
@@ -5466,29 +5960,31 @@
           <t>@yuzenmatcha</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>Gully Labs</t>
+      <c r="C93" s="51" t="inlineStr">
+        <is>
+          <t>🏢 Brand / Media Partner</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
+          <t>Gully Labs</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
           <t>Yūzen Matcha 友禅抹茶</t>
         </is>
       </c>
-      <c r="E93" s="22" t="inlineStr">
+      <c r="F93" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F93" s="22" t="inlineStr">
+      <c r="G93" s="22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G93" s="13" t="n">
-        <v>0</v>
-      </c>
       <c r="H93" s="13" t="n">
         <v>0</v>
       </c>
@@ -5496,18 +5992,21 @@
         <v>0</v>
       </c>
       <c r="J93" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="13" t="n">
         <v>447</v>
       </c>
-      <c r="K93" s="13" t="n">
+      <c r="L93" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="L93" s="14" t="n">
+      <c r="M93" s="14" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
